--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487697_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487697_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.7484</v>
+        <v>14.6037</v>
       </c>
       <c r="E2" t="n">
-        <v>9.398099999999999</v>
+        <v>10.1989</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3503</v>
+        <v>4.4048</v>
       </c>
       <c r="G2" t="n">
         <v>11.0439</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2194</v>
+        <v>0.6359</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9691</v>
+        <v>-0.1683</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7497</v>
+        <v>0.8042</v>
       </c>
       <c r="V2" t="n">
         <v>2.7298</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.757099999999999</v>
+        <v>7.7204</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7281</v>
+        <v>5.1275</v>
       </c>
       <c r="F3" t="n">
-        <v>3.029</v>
+        <v>2.5929</v>
       </c>
       <c r="G3" t="n">
         <v>0.7352</v>
@@ -688,13 +688,13 @@
         <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3517</v>
+        <v>1.3151</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1541</v>
+        <v>0.5535</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1977</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>3.3418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.3992</v>
+        <v>5.8972</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0778</v>
+        <v>4.2761</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3214</v>
+        <v>1.6212</v>
       </c>
       <c r="G4" t="n">
         <v>3.3782</v>
@@ -766,13 +766,13 @@
         <v>2.1344</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8569</v>
+        <v>1.3549</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5493</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3076</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.49</v>
+        <v>2.0629</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4903</v>
+        <v>0.3902</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9997</v>
+        <v>1.6726</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2605</v>
@@ -844,13 +844,13 @@
         <v>2.1344</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1268</v>
+        <v>0.6996</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1233</v>
+        <v>0.0232</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0034</v>
+        <v>0.6764</v>
       </c>
       <c r="V5" t="n">
         <v>2.4</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARTÍN FERNÁNDEZ</t>
+          <t>D. CARABALLO ROPERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7057</v>
+        <v>0.5958</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4568</v>
+        <v>-0.9298</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2489</v>
+        <v>1.5256</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1656</v>
+        <v>0.5263</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1013</v>
+        <v>0.0503</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2669</v>
+        <v>0.476</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0288</v>
+        <v>0.143</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0288</v>
+        <v>0.0618</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1944</v>
+        <v>0.3833</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0725</v>
+        <v>-0.0115</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2669</v>
+        <v>0.3948</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5401</v>
+        <v>0.4576</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4856</v>
+        <v>-0.1026</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0545</v>
+        <v>0.5602</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CARABALLO ROPERO</t>
+          <t>A. MARTÍN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4229</v>
+        <v>0.3871</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.13</v>
+        <v>0.0564</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5529</v>
+        <v>0.3307</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5263</v>
+        <v>0.1656</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0503</v>
+        <v>-0.1013</v>
       </c>
       <c r="I7" t="n">
-        <v>0.476</v>
+        <v>0.2669</v>
       </c>
       <c r="J7" t="n">
-        <v>0.143</v>
+        <v>-0.0288</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0618</v>
+        <v>-0.0288</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3833</v>
+        <v>0.1944</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0115</v>
+        <v>-0.0725</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3948</v>
+        <v>0.2669</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5821</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2847</v>
+        <v>0.2215</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>0.0852</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5875</v>
+        <v>0.1363</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1522</v>
+        <v>-0.8519</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2896</v>
+        <v>0.5899</v>
       </c>
       <c r="F8" t="n">
         <v>-1.4418</v>
@@ -1078,10 +1078,10 @@
         <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.194</v>
+        <v>0.1063</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0606</v>
+        <v>0.2397</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1335</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5517</v>
+        <v>-1.906</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.402</v>
+        <v>-4.0016</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8503</v>
+        <v>2.0956</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5227</v>
@@ -1156,13 +1156,13 @@
         <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2245</v>
+        <v>0.4212</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3623</v>
+        <v>0.0381</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1378</v>
+        <v>0.3831</v>
       </c>
       <c r="V9" t="n">
         <v>1.5537</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6725</v>
+        <v>-3.1713</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0596</v>
+        <v>-3.6778</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6129</v>
+        <v>0.5065</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6282</v>
+        <v>0.0034</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0593</v>
+        <v>0.4844</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5689</v>
+        <v>-0.4811</v>
       </c>
       <c r="J10" t="n">
-        <v>0.123</v>
+        <v>-0.1609</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0824</v>
+        <v>1.0875</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0406</v>
+        <v>-1.2484</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5052</v>
+        <v>0.1643</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0231</v>
+        <v>-0.6031</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5283</v>
+        <v>0.7674</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7463</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R10" t="n">
-        <v>0.194</v>
+        <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1754</v>
+        <v>0.2327</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2423</v>
+        <v>-0.2288</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4177</v>
+        <v>0.4616</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7298</v>
+        <v>-2.8254</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7298</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1629</v>
+        <v>-3.3539</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4786</v>
+        <v>-1.6592</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3157</v>
+        <v>-1.6947</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0034</v>
+        <v>0.6282</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4844</v>
+        <v>0.0593</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4811</v>
+        <v>0.5689</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1609</v>
+        <v>0.123</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0875</v>
+        <v>0.0824</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2484</v>
+        <v>0.0406</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1643</v>
+        <v>0.5052</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6031</v>
+        <v>-0.0231</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7674</v>
+        <v>0.5283</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5821</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3284</v>
+        <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7588</v>
+        <v>0.4941</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0296</v>
+        <v>0.1581</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2708</v>
+        <v>0.3359</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.8254</v>
+        <v>-2.7298</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4477</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>21.984</v>
+        <v>21.98400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3705</v>
+        <v>10.3706</v>
       </c>
       <c r="F12" t="n">
-        <v>11.6135</v>
+        <v>11.6134</v>
       </c>
       <c r="G12" t="n">
         <v>13.1573</v>
@@ -1369,7 +1369,7 @@
         <v>8.947300000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>2.8644</v>
+        <v>2.864399999999999</v>
       </c>
       <c r="M12" t="n">
         <v>1.3454</v>
@@ -1390,7 +1390,7 @@
         <v>13.5824</v>
       </c>
       <c r="S12" t="n">
-        <v>5.938899999999999</v>
+        <v>5.9389</v>
       </c>
       <c r="T12" t="n">
         <v>1.3456</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8767</v>
+        <v>4.7038</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5706</v>
+        <v>3.3704</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3061</v>
+        <v>1.3333</v>
       </c>
       <c r="G13" t="n">
         <v>2.3036</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3329</v>
+        <v>-0.5058</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0584</v>
+        <v>-0.2586</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2745</v>
+        <v>-0.2473</v>
       </c>
       <c r="V13" t="n">
         <v>0.7716</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0752</v>
+        <v>0.0296</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2859</v>
+        <v>3.1858</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2106</v>
+        <v>-3.1561</v>
       </c>
       <c r="G14" t="n">
         <v>1.0912</v>
@@ -1546,13 +1546,13 @@
         <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7028</v>
+        <v>-0.7484</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.544</v>
+        <v>-0.6441</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1588</v>
+        <v>-0.1043</v>
       </c>
       <c r="V14" t="n">
         <v>1.0451</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.517</v>
+        <v>-1.2529</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7538</v>
+        <v>-0.3534</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7632</v>
+        <v>-0.8995</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6364</v>
@@ -1624,13 +1624,13 @@
         <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5641</v>
+        <v>-0.3</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5451</v>
+        <v>-0.1447</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0191</v>
+        <v>-0.1553</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1224</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6181</v>
+        <v>-1.7911</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2821</v>
+        <v>-1.4823</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3361</v>
+        <v>-0.3088</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5165</v>
@@ -1702,13 +1702,13 @@
         <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5393</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3623</v>
+        <v>-0.5625</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.177</v>
+        <v>-0.1497</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3385</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8594</v>
+        <v>-2.0413</v>
       </c>
       <c r="E17" t="n">
-        <v>1.704</v>
+        <v>1.6039</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5634</v>
+        <v>-3.6451</v>
       </c>
       <c r="G17" t="n">
         <v>1.7782</v>
@@ -1780,13 +1780,13 @@
         <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2362</v>
+        <v>-0.4181</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.12</v>
+        <v>-0.2201</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1162</v>
+        <v>-0.1979</v>
       </c>
       <c r="V17" t="n">
         <v>-4.5656</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6477</v>
+        <v>-2.5204</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4783</v>
+        <v>-2.3782</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1695</v>
+        <v>-0.1422</v>
       </c>
       <c r="G18" t="n">
         <v>-3.0833</v>
@@ -1858,13 +1858,13 @@
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4181</v>
+        <v>-0.2908</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3028</v>
+        <v>-0.2027</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.6597</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6853</v>
+        <v>-3.4617</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2038</v>
+        <v>-2.9024</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4815</v>
+        <v>-0.5593</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1433</v>
+        <v>-1.8522</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4498</v>
+        <v>-0.2167</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5932</v>
+        <v>-1.6355</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5056</v>
+        <v>-0.4837</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3924</v>
+        <v>0.0618</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.898</v>
+        <v>-0.5455</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6377</v>
+        <v>-1.3685</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9425</v>
+        <v>-0.2785</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6952</v>
+        <v>-1.09</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3881</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5523</v>
+        <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4726</v>
+        <v>-0.0572</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1839</v>
+        <v>-0.2843</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2887</v>
+        <v>0.2271</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4027</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7982</v>
+        <v>-3.7765</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1026</v>
+        <v>-1.8044</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6955</v>
+        <v>-1.9721</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8522</v>
+        <v>-2.1433</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2167</v>
+        <v>0.4498</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6355</v>
+        <v>-2.5932</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4837</v>
+        <v>-0.5056</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0618</v>
+        <v>1.3924</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5455</v>
+        <v>-1.898</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3685</v>
+        <v>-1.6377</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2785</v>
+        <v>-0.9425</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.09</v>
+        <v>-0.6952</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3937</v>
+        <v>-0.6185</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4845</v>
+        <v>-0.4167</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.2019</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.4027</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.6848</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2968</v>
+        <v>-4.8514</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.6545</v>
+        <v>-5.4543</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3577</v>
+        <v>0.603</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1396</v>
@@ -2092,13 +2092,13 @@
         <v>2.7164</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2665</v>
+        <v>-0.821</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.968</v>
+        <v>-0.7678</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2985</v>
+        <v>-0.0532</v>
       </c>
       <c r="V21" t="n">
         <v>0.2734</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5133</v>
+        <v>-7.0222</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6988</v>
+        <v>-5.3985</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8145</v>
+        <v>-1.6237</v>
       </c>
       <c r="G22" t="n">
         <v>-5.9588</v>
@@ -2170,13 +2170,13 @@
         <v>2.7164</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9578</v>
+        <v>-1.4667</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3919</v>
+        <v>-1.0916</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5659</v>
+        <v>-0.3751</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1788</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-21.9839</v>
+        <v>-21.9841</v>
       </c>
       <c r="E23" t="n">
         <v>-11.6134</v>
@@ -2248,13 +2248,13 @@
         <v>14.5524</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.9388</v>
+        <v>-5.938700000000001</v>
       </c>
       <c r="T23" t="n">
         <v>-4.5931</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3458</v>
+        <v>-1.3456</v>
       </c>
       <c r="V23" t="n">
         <v>-3.8582</v>
